--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>1289</v>
+        <v>2040</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
-        <v>5241</v>
+        <v>2829</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -532,10 +532,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>2383</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>3478</v>
+        <v>2455</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" t="n">
-        <v>1761</v>
+        <v>3154</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E9" t="n">
-        <v>2562</v>
+        <v>2279</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
-        <v>1314</v>
+        <v>471</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>1062</v>
+        <v>1081</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="E12" t="n">
-        <v>3081</v>
+        <v>3398</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E13" t="n">
-        <v>2974</v>
+        <v>3645</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>913</v>
+        <v>596</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E15" t="n">
-        <v>1731</v>
+        <v>1813</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E16" t="n">
-        <v>2277</v>
+        <v>2259</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>393</v>
+        <v>570</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1152,10 +1152,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,10 +1218,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1251,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,10 +1317,10 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>1870</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1350,10 +1350,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1383,21 +1383,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,21 +1416,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>706</v>
+        <v>807</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -1614,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1647,10 +1647,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1677,20 +1677,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>1940</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1713,10 +1713,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
@@ -1782,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1812,10 +1812,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1845,10 +1845,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1881,7 +1881,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1944,21 +1944,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1977,21 +1977,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2010,21 +2010,21 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>2355</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2043,21 +2043,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2109,10 +2109,10 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -2241,21 +2241,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2274,7 +2274,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>45</v>
@@ -2307,21 +2307,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2373,10 +2373,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -2406,10 +2406,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -2439,21 +2439,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -2472,21 +2472,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2505,10 +2505,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -2571,21 +2571,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2604,10 +2604,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2637,21 +2637,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2670,21 +2670,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2703,10 +2703,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2736,21 +2736,21 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2868,10 +2868,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -2904,7 +2904,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2934,21 +2934,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2970,7 +2970,7 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>342</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -3000,10 +3000,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -3036,18 +3036,18 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>435</v>
+        <v>283</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -3099,10 +3099,10 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -3135,7 +3135,7 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3153,31 +3153,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>385</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -3264,21 +3288,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3294,24 +3318,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3327,24 +3351,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3360,24 +3384,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>1717</v>
+        <v>440</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3393,20 +3417,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3426,24 +3450,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3459,24 +3483,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3492,24 +3516,24 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3525,24 +3549,24 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3558,24 +3582,24 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -3591,24 +3615,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>1160</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -3726,21 +3750,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>1127</v>
+        <v>1660</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3759,10 +3783,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3792,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3924,10 +3948,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3957,10 +3981,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -3990,10 +4014,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4023,21 +4047,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4056,10 +4080,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4122,10 +4146,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>4903</v>
+        <v>2216</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4155,21 +4179,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>379</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -4221,21 +4245,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -4353,10 +4377,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4386,21 +4410,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4452,21 +4476,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4485,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>810</v>
+        <v>112</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4518,10 +4542,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4650,10 +4674,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>3204</v>
+        <v>2227</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -4683,21 +4707,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4716,10 +4740,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4845,10 +4869,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -4858,11 +4882,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4878,20 +4902,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4914,21 +4938,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>201</v>
+        <v>750</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4947,10 +4971,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -4980,10 +5004,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>650</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -5013,10 +5037,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -5046,10 +5070,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>160</v>
+        <v>305</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5072,10 +5096,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>634</v>
+        <v>531</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -5235,21 +5259,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5328,7 +5352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5400,10 +5424,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5421,62 +5445,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Adabraka</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emmanuel Otiboe</t>
+          <t>Zephaniah Lartey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>272</v>
+        <v>230</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zephaniah Lartey</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5487,29 +5511,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>39</v>
+      </c>
+      <c r="E6" t="n">
+        <v>582</v>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>130</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5520,12 +5544,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5535,47 +5559,47 @@
         <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>970</v>
+        <v>465</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -5586,29 +5610,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5619,29 +5643,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>UssherFort</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Seth Kpelebe</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>465</v>
+        <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -5652,29 +5676,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Yours and Ours</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Prince Odum</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -5685,64 +5709,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Prince Odum</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -5829,21 +5820,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5862,21 +5853,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5895,10 +5886,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -5928,10 +5919,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5997,18 +5988,18 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -6027,21 +6018,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -6060,10 +6051,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -6096,7 +6087,7 @@
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -6126,21 +6117,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6159,21 +6150,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6192,21 +6183,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -6225,21 +6216,21 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>2040</v>
+        <v>964</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="E4" t="n">
-        <v>2829</v>
+        <v>1402</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>2383</v>
+        <v>1535</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>2455</v>
+        <v>402</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E7" t="n">
-        <v>3154</v>
+        <v>1789</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +628,13 @@
         <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E9" t="n">
-        <v>2279</v>
+        <v>1379</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>1081</v>
+        <v>480</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -700,10 +700,10 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="E12" t="n">
-        <v>3398</v>
+        <v>2710</v>
       </c>
       <c r="F12" t="n">
         <v>20</v>
@@ -724,13 +724,13 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E13" t="n">
-        <v>3645</v>
+        <v>3893</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E14" t="n">
-        <v>596</v>
+        <v>692</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E15" t="n">
-        <v>1813</v>
+        <v>2629</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="E16" t="n">
-        <v>2259</v>
+        <v>2917</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>570</v>
+        <v>390</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>336</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1155,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,10 +1218,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1284,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1870</v>
+        <v>520</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1353,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1383,21 +1383,21 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,10 +1416,10 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1449,10 +1449,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1482,10 +1482,10 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>807</v>
+        <v>365</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -1614,21 +1614,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1644,20 +1644,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1677,20 +1677,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>1920</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1713,10 +1713,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1746,10 +1746,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1779,10 +1779,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1815,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1845,7 +1845,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>40</v>
@@ -1878,10 +1878,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1944,21 +1944,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2010,21 +2010,21 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>2355</v>
+        <v>1000</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2043,10 +2043,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -2112,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -2244,7 +2244,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2274,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -2307,21 +2307,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2373,21 +2373,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2406,10 +2406,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -2472,21 +2472,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -2604,10 +2604,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2637,21 +2637,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2670,21 +2670,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2703,10 +2703,10 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -2736,21 +2736,21 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2868,21 +2868,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>345</v>
+        <v>654</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2901,10 +2901,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2934,21 +2934,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>795</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2967,10 +2967,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -3000,21 +3000,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3033,21 +3033,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>555</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -3099,21 +3099,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3132,10 +3132,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3153,55 +3153,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>33</v>
-      </c>
-      <c r="E12" t="n">
-        <v>385</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3216,7 +3192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3288,7 +3264,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>60</v>
@@ -3321,10 +3297,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3354,21 +3330,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3387,21 +3363,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>440</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3420,21 +3396,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3456,18 +3432,18 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3486,21 +3462,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3522,18 +3498,18 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3552,21 +3528,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3585,10 +3561,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3618,10 +3594,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>1160</v>
+        <v>498</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -3639,31 +3615,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14">
-        <f>SUM(C3:C13)</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>SUM(E3:E13)</f>
-        <v/>
-      </c>
-      <c r="F14">
-        <f>SUM(F3:F13)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>F14&amp;"/"&amp;C14</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>SUM(H3:H13)</f>
+      <c r="C15">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>F15&amp;"/"&amp;C15</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUM(H3:H14)</f>
         <v/>
       </c>
     </row>
@@ -3750,21 +3750,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>1660</v>
+        <v>805</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3783,10 +3783,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3816,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3948,10 +3948,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3981,21 +3981,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4014,21 +4014,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4047,21 +4047,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>568</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4080,10 +4080,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4146,10 +4146,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
-        <v>2216</v>
+        <v>546</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -4179,21 +4179,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>379</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -4212,10 +4212,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -4245,21 +4245,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -4377,10 +4377,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4410,10 +4410,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>2000</v>
+        <v>1235</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4476,21 +4476,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4509,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -4542,10 +4542,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -4674,21 +4674,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2227</v>
+        <v>150</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4707,10 +4707,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -4740,10 +4740,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4800,7 +4800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4875,7 +4875,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4905,21 +4905,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4938,21 +4938,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>750</v>
+        <v>355</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4971,21 +4971,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5004,21 +5004,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>650</v>
+        <v>1261</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5037,21 +5037,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5070,76 +5070,52 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E10" t="n">
-        <v>531</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>F11&amp;"/"&amp;C11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(H3:H10)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -5259,21 +5235,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5352,7 +5328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5424,7 +5400,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>60</v>
@@ -5457,7 +5433,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
         <v>230</v>
@@ -5487,20 +5463,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>182</v>
+        <v>339</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5520,24 +5496,24 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
-        <v>39</v>
-      </c>
-      <c r="E6" t="n">
-        <v>582</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5553,20 +5529,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>465</v>
+        <v>170</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5589,10 +5565,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -5622,10 +5598,10 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -5655,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>110</v>
@@ -5676,64 +5652,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prince Odum</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>230</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2/2</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -5820,21 +5763,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5853,21 +5796,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5886,21 +5829,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5919,10 +5862,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5985,21 +5928,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -6021,18 +5964,18 @@
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -6051,21 +5994,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -6084,21 +6027,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -6117,21 +6060,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6150,21 +6093,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6183,21 +6126,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,10 +484,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>964</v>
+        <v>620</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -508,13 +508,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>1402</v>
+        <v>584</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>1535</v>
+        <v>1233</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>402</v>
+        <v>260</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="n">
-        <v>1789</v>
+        <v>949</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="E9" t="n">
-        <v>1379</v>
+        <v>1349</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>480</v>
+        <v>135</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
-        <v>480</v>
+        <v>522</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E12" t="n">
-        <v>2710</v>
+        <v>1035</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E13" t="n">
-        <v>3893</v>
+        <v>944</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>692</v>
+        <v>395</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>2629</v>
+        <v>1099</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" t="n">
-        <v>2917</v>
+        <v>2231</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -888,10 +888,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,21 +1119,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1155,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1185,10 +1185,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -1218,10 +1218,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1272,45 +1272,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Richard Manu</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>1500</v>
+        <v>170</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>GTUC Allos 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Sylvester Ntumy</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1320,7 +1320,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>520</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1338,29 +1338,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
+          <t>GTUC Main Campus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sylvester Ntumy</t>
+          <t>Jeremiah Ashong</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1371,163 +1371,130 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GTUC Main Campus</t>
+          <t>Kings University</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jeremiah Ashong</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kings University</t>
+          <t>Korle Bu Light</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Sonia Elolo</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Korle Bu Light</t>
+          <t>Regent University</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sonia Elolo</t>
+          <t>Prince Forson</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>247</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Regent University</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>26</v>
-      </c>
-      <c r="E14" t="n">
-        <v>365</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15">
-        <f>SUM(C3:C14)</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>SUM(E3:E14)</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>SUM(F3:F14)</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>F15&amp;"/"&amp;C15</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>SUM(H3:H14)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -1542,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,21 +1581,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1647,21 +1614,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1680,10 +1647,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>1920</v>
+        <v>190</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -1710,20 +1677,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1734,29 +1701,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Block A Beta</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gracy Wellington</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1767,29 +1734,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1800,22 +1767,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1833,95 +1800,95 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>111</v>
+      </c>
+      <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
-        <v>20</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1932,62 +1899,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1998,163 +1965,130 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Vacation Church</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Antoinette Annan</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/14</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Volta Annex New</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stephanie Seglah</t>
+          <t>Esllah Osei</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>13</v>
-      </c>
-      <c r="E18" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19">
-        <f>SUM(C3:C18)</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>SUM(D3:D18)</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>SUM(E3:E18)</f>
-        <v/>
-      </c>
-      <c r="F19">
-        <f>SUM(F3:F18)</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>F19&amp;"/"&amp;C19</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>SUM(H3:H18)</f>
+      <c r="C18">
+        <f>SUM(C3:C17)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>SUM(D3:D17)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>SUM(E3:E17)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>SUM(F3:F17)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>F18&amp;"/"&amp;C18</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUM(H3:H17)</f>
         <v/>
       </c>
     </row>
@@ -2241,21 +2175,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2274,21 +2208,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2307,21 +2241,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2340,10 +2274,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -2373,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -2406,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2472,10 +2406,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -2571,21 +2505,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2604,10 +2538,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -2637,21 +2571,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2703,21 +2637,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
-        <v>90</v>
-      </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2736,21 +2670,21 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -2868,21 +2802,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>654</v>
+        <v>550</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2901,10 +2835,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2934,21 +2868,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>795</v>
+        <v>250</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2967,21 +2901,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3033,10 +2967,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -3066,21 +3000,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>555</v>
+        <v>227</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3099,10 +3033,10 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -3132,21 +3066,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3264,21 +3198,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3297,21 +3231,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3330,10 +3264,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -3363,21 +3297,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3396,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
@@ -3429,21 +3363,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3462,21 +3396,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3495,10 +3429,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -3528,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -3561,10 +3495,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3594,10 +3528,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>498</v>
+        <v>259</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -3620,10 +3554,10 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E14" t="n">
-        <v>1460</v>
+        <v>1305</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -3750,21 +3684,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>805</v>
+        <v>420</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3786,7 +3720,7 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3816,21 +3750,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3948,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -3981,21 +3915,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4014,21 +3948,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4047,10 +3981,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>568</v>
+        <v>175</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -4080,10 +4014,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4146,21 +4080,21 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>546</v>
+        <v>132</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -4179,10 +4113,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -4212,10 +4146,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -4305,7 +4239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4377,10 +4311,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4407,53 +4341,53 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>1235</v>
+        <v>920</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Haatso Executive</t>
+          <t>Haatso West</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stephen Mensah</t>
+          <t>Michael Sarpong</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4464,130 +4398,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Haatso Melcom</t>
+          <t>THS Westland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kenneth Koomson</t>
+          <t>Joseph Halivor</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Haatso West</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Michael Sarpong</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" t="n">
-        <v>102</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>THS Westland</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Joseph Halivor</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>21</v>
-      </c>
-      <c r="E8" t="n">
-        <v>78</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9">
-        <f>SUM(C3:C8)</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>SUM(D3:D8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E3:E8)</f>
-        <v/>
-      </c>
-      <c r="F9">
-        <f>SUM(F3:F8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>F9&amp;"/"&amp;C9</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>SUM(H3:H8)</f>
+      <c r="C7">
+        <f>SUM(C3:C6)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7&amp;"/"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(H3:H6)</f>
         <v/>
       </c>
     </row>
@@ -4674,10 +4542,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4707,21 +4575,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4740,21 +4608,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4800,7 +4668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4872,10 +4740,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4905,10 +4773,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -4938,21 +4806,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>355</v>
+        <v>270</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5004,21 +4872,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>1261</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5037,21 +4905,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5070,52 +4938,76 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>173</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -5328,7 +5220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5400,7 +5292,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>60</v>
@@ -5433,10 +5325,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -5463,20 +5355,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>339</v>
+        <v>130</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5496,86 +5388,86 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>297</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>ATU YWCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Emmanuel Otiboe</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -5586,29 +5478,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>270</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5619,29 +5511,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -5652,31 +5544,64 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>F11&amp;"/"&amp;C11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(H3:H10)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -5763,21 +5688,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5799,7 +5724,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -5862,10 +5787,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5895,21 +5820,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5928,21 +5853,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5961,21 +5886,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5997,7 +5922,7 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -6060,21 +5985,21 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>30</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2/7</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -6093,21 +6018,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -6126,21 +6051,21 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>620</v>
+        <v>1600</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -505,16 +505,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>584</v>
+        <v>1342</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>1233</v>
+        <v>438</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E7" t="n">
-        <v>949</v>
+        <v>1307</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E9" t="n">
-        <v>1349</v>
+        <v>3061</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>253</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>522</v>
+        <v>380</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E12" t="n">
-        <v>1035</v>
+        <v>4118</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E13" t="n">
-        <v>944</v>
+        <v>2653</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
-        <v>395</v>
+        <v>291</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
-        <v>1099</v>
+        <v>1995</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E16" t="n">
-        <v>2231</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -891,18 +891,18 @@
         <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,21 +987,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1119,21 +1119,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1152,10 +1152,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -1185,10 +1185,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -1218,10 +1218,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -1284,21 +1284,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>170</v>
+        <v>670</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>2830</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -1416,21 +1416,21 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>140</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3/9</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>6</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1449,21 +1449,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>247</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1581,21 +1581,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1614,10 +1614,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1647,10 +1647,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>190</v>
+        <v>1828</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -1680,21 +1680,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1713,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1749,7 +1749,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1779,21 +1779,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1812,21 +1812,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1848,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1878,21 +1878,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1911,10 +1911,10 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1944,21 +1944,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1977,10 +1977,10 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -2010,21 +2010,21 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>0/14</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2043,10 +2043,10 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -2178,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -2241,21 +2241,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2277,7 +2277,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2406,10 +2406,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -2505,21 +2505,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -2538,21 +2538,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2571,21 +2571,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2604,21 +2604,21 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -2637,21 +2637,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2802,10 +2802,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>550</v>
+        <v>284</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -2835,21 +2835,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>250</v>
@@ -2901,21 +2901,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2967,10 +2967,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -3000,21 +3000,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>227</v>
+        <v>1246</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3033,10 +3033,10 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -3066,21 +3066,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3201,7 +3201,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -3231,17 +3231,17 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3261,24 +3261,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3294,20 +3294,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
@@ -3363,7 +3363,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>85</v>
@@ -3396,21 +3396,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3429,10 +3429,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -3462,21 +3462,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3495,10 +3495,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -3525,24 +3525,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>259</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -3554,10 +3554,10 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
-        <v>1305</v>
+        <v>500</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -3684,21 +3684,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>420</v>
+        <v>1520</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3717,10 +3717,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3810,7 +3810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -3912,119 +3912,119 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abundant Life West</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eshal Gabriel</t>
+          <t>Vicentia Boakye</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Deacon's Academy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vicentia Boakye</t>
+          <t>Gideon Boateng</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deacon's Academy</t>
+          <t>Dome Main</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gideon Boateng</t>
+          <t>John Amoako</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4035,62 +4035,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dome Main</t>
+          <t>Dome Ministries</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>John Amoako</t>
+          <t>Wilhermina Teprey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dome Ministries</t>
+          <t>Dome North</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wilhermina Teprey</t>
+          <t>Pearl Addo</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -4101,130 +4101,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dome North</t>
+          <t>Kisseman</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pearl Addo</t>
+          <t>Victoria Affran</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kisseman</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Victoria Affran</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>20</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/2</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Taifa Burkina</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Samuel Brown</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -4314,7 +4248,7 @@
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4344,21 +4278,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4377,10 +4311,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>224</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4410,10 +4344,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -4539,24 +4473,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4572,7 +4506,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4585,11 +4519,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4605,24 +4539,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4740,10 +4674,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4773,21 +4707,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>738</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4809,7 +4743,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -4839,21 +4773,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4872,10 +4806,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -4905,21 +4839,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4938,10 +4872,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -4964,10 +4898,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -5292,7 +5226,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>60</v>
@@ -5325,21 +5259,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>221</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5358,21 +5292,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5391,10 +5325,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>297</v>
+        <v>2215</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -5427,7 +5361,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -5457,10 +5391,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -5490,10 +5424,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5523,10 +5457,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -5556,7 +5490,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>100</v>
@@ -5688,21 +5622,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5721,21 +5655,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5787,7 +5721,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
@@ -5820,21 +5754,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5853,21 +5787,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5886,21 +5820,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5919,10 +5853,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -6018,21 +5952,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1342</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1307</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3061</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>4118</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2653</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1995</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -987,21 +987,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1119,21 +1119,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1152,21 +1152,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,21 +1218,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1251,21 +1251,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1284,21 +1284,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>670</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1/5</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2830</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,21 +1350,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1383,21 +1383,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,21 +1416,21 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>0/9</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1449,21 +1449,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1581,21 +1581,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1614,21 +1614,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1647,21 +1647,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1828</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1680,21 +1680,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1713,21 +1713,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1746,21 +1746,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1779,21 +1779,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1812,21 +1812,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1845,21 +1845,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1878,21 +1878,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1944,21 +1944,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>40</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1977,21 +1977,21 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2043,21 +2043,21 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2175,21 +2175,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2274,21 +2274,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2307,21 +2307,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2340,21 +2340,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -2406,21 +2406,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2439,21 +2439,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2538,21 +2538,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2571,21 +2571,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2637,21 +2637,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2802,21 +2802,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2845,11 +2845,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -2868,21 +2868,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2901,21 +2901,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2967,21 +2967,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3000,21 +3000,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>7</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>7/7</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3033,21 +3033,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3066,21 +3066,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3126,7 +3126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3198,21 +3198,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3231,21 +3231,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3264,21 +3264,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3297,21 +3297,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3330,21 +3330,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3363,21 +3363,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3396,21 +3396,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3429,21 +3429,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3462,21 +3462,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3495,21 +3495,21 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -3528,76 +3528,52 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>41</v>
-      </c>
-      <c r="E14" t="n">
-        <v>500</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15">
-        <f>SUM(C3:C14)</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>SUM(E3:E14)</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>SUM(F3:F14)</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>F15&amp;"/"&amp;C15</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>SUM(H3:H14)</f>
+      <c r="C14">
+        <f>SUM(C3:C13)</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUM(D3:D13)</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUM(E3:E13)</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUM(F3:F13)</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>F14&amp;"/"&amp;C14</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
     </row>
@@ -3684,21 +3660,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1520</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3717,21 +3693,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3810,7 +3786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3882,21 +3858,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3915,21 +3891,21 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3948,21 +3924,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3981,37 +3957,37 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dome Main</t>
+          <t>Dome Ministries</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>John Amoako</t>
+          <t>Wilhermina Teprey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -4024,73 +4000,73 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/0</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dome Ministries</t>
+          <t>Dome North</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wilhermina Teprey</t>
+          <t>Pearl Addo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dome North</t>
+          <t>Kisseman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pearl Addo</t>
+          <t>Victoria Affran</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -4101,64 +4077,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kisseman</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Victoria Affran</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>40</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>F11&amp;"/"&amp;C11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(H3:H10)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -4245,21 +4188,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4311,21 +4254,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4344,21 +4287,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4476,21 +4419,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4542,21 +4485,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4602,7 +4545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4674,21 +4617,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4707,21 +4650,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>738</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4740,21 +4683,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4773,21 +4716,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4806,21 +4749,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4839,21 +4782,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4872,76 +4815,52 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="D10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E10" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>F11&amp;"/"&amp;C11</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>SUM(H3:H10)</f>
+      <c r="C10">
+        <f>SUM(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D3:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E3:E9)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUM(F3:F9)</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>F10&amp;"/"&amp;C10</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUM(H3:H9)</f>
         <v/>
       </c>
     </row>
@@ -5226,21 +5145,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5259,21 +5178,21 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5292,21 +5211,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5325,21 +5244,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2215</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>4</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5358,21 +5277,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5391,21 +5310,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5424,21 +5343,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5457,21 +5376,21 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5/5</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5490,21 +5409,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -5622,21 +5541,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5655,21 +5574,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5721,21 +5640,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5787,21 +5706,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5853,21 +5772,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5952,21 +5871,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1355</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>6846</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2985</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3576</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3594</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3138</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +652,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4406</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>4537</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -888,21 +888,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -987,21 +987,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>719</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1119,21 +1119,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1152,21 +1152,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,21 +1218,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1251,21 +1251,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1284,21 +1284,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2330</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,21 +1350,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1383,21 +1383,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1413,24 +1413,24 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1449,21 +1449,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1614,21 +1614,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1647,21 +1647,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1680,21 +1680,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1713,21 +1713,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1779,21 +1779,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1812,21 +1812,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1911,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1944,21 +1944,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -1977,21 +1977,21 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2043,21 +2043,21 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -2175,21 +2175,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2406,21 +2406,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2538,21 +2538,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2571,21 +2571,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2730,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ruby Nelson</t>
+          <t>Tracy Osei</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Calebina Ikhayere</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Jonathan Ephraim</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3087,31 +3087,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>280</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12">
-        <f>SUM(C3:C11)</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>SUM(D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>SUM(E3:E11)</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>SUM(F3:F11)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>F12&amp;"/"&amp;C12</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>SUM(H3:H11)</f>
+      <c r="C13">
+        <f>SUM(C3:C12)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUM(D3:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E3:E12)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13&amp;"/"&amp;C13</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H3:H12)</f>
         <v/>
       </c>
     </row>
@@ -3195,24 +3219,24 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3" t="n">
+        <v>270</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3231,21 +3255,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3261,24 +3285,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3297,21 +3321,21 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3330,21 +3354,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -3363,21 +3387,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3393,24 +3417,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3429,21 +3453,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3462,21 +3486,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3495,56 +3519,47 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UMC E-Church</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Divine Olubakinde</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2997</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3660,21 +3675,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3693,21 +3708,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3726,21 +3741,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3858,21 +3873,21 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3891,21 +3906,21 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3924,21 +3939,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3957,21 +3972,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>451</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3990,21 +4005,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>5362</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4023,21 +4038,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4056,21 +4071,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -4188,21 +4203,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4221,21 +4236,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4254,21 +4269,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4287,21 +4302,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4419,21 +4434,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3286</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4452,21 +4467,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4485,21 +4500,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4650,21 +4665,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1589</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4716,21 +4731,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1960</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4815,21 +4830,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5145,21 +5160,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5175,24 +5190,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>8/7</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -5211,21 +5226,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5244,21 +5259,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1462</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5277,21 +5292,21 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -5310,21 +5325,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5343,21 +5358,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -5376,21 +5391,21 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5409,21 +5424,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -5640,21 +5655,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5772,21 +5787,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -5871,21 +5886,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -484,13 +484,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>1355</v>
+        <v>1225</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +508,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>6846</v>
+        <v>1336</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +532,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>2985</v>
+        <v>634</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>3576</v>
+        <v>632</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +580,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E7" t="n">
-        <v>3594</v>
+        <v>2904</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -628,13 +628,13 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E9" t="n">
-        <v>3138</v>
+        <v>1882</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -652,10 +652,10 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -676,13 +676,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>1059</v>
+        <v>606</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +700,13 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="E12" t="n">
-        <v>4406</v>
+        <v>1004</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -724,13 +724,13 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="E13" t="n">
-        <v>1935</v>
+        <v>3043</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -748,13 +748,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>280</v>
+        <v>1310</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="E16" t="n">
-        <v>4537</v>
+        <v>4547</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -888,10 +888,10 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>340</v>
+        <v>291</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -954,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>719</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -1119,10 +1119,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -1152,21 +1152,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1185,21 +1185,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1221,7 +1221,7 @@
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
@@ -1284,10 +1284,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>975</v>
+        <v>470</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1317,21 +1317,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>2330</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,21 +1350,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1383,21 +1383,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,21 +1416,21 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1449,21 +1449,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>766</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1581,21 +1581,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1614,21 +1614,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1647,21 +1647,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>119</v>
+        <v>1900</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1713,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1746,21 +1746,21 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1779,21 +1779,21 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1812,21 +1812,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1845,21 +1845,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1878,21 +1878,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -1911,10 +1911,10 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1944,10 +1944,10 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>1000</v>
+        <v>485</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1977,7 +1977,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
@@ -2043,10 +2043,10 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>235</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -2175,21 +2175,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2406,21 +2406,21 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -2439,21 +2439,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -2472,21 +2472,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -2538,21 +2538,21 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -2571,21 +2571,21 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -2730,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,21 +2802,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2868,21 +2868,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2901,21 +2901,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -2934,21 +2934,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -2967,21 +2967,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3000,21 +3000,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3033,21 +3033,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3066,76 +3066,52 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" t="n">
-        <v>280</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Council Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13">
-        <f>SUM(C3:C12)</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>SUM(D3:D12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>SUM(E3:E12)</f>
-        <v/>
-      </c>
-      <c r="F13">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>F13&amp;"/"&amp;C13</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>SUM(H3:H12)</f>
+      <c r="C12">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUM(D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUM(E3:E11)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUM(F3:F11)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12&amp;"/"&amp;C12</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
         <v/>
       </c>
     </row>
@@ -3222,21 +3198,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>270</v>
+        <v>2317</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3255,21 +3231,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3288,10 +3264,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -3321,7 +3297,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
@@ -3354,10 +3330,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3387,21 +3363,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3420,21 +3396,21 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>295</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3456,7 +3432,7 @@
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -3486,21 +3462,21 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3519,10 +3495,10 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -3545,10 +3521,10 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E13" t="n">
-        <v>2997</v>
+        <v>1645</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -3675,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>725</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3708,10 +3684,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3741,21 +3717,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3876,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3906,10 +3882,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -3939,21 +3915,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3972,21 +3948,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>451</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4005,21 +3981,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>5362</v>
+        <v>1096</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4041,7 +4017,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>585</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -4071,21 +4047,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -4203,10 +4179,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -4236,21 +4212,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4269,10 +4245,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1620</v>
+        <v>312</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4302,10 +4278,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>1027</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -4437,18 +4413,18 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>212</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4467,21 +4443,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4500,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -4560,7 +4536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4632,21 +4608,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4665,21 +4641,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>1589</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4698,21 +4674,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4731,21 +4707,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>1960</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4797,21 +4773,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4830,52 +4806,76 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>270</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1585</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10">
-        <f>SUM(C3:C9)</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>SUM(D3:D9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>SUM(E3:E9)</f>
-        <v/>
-      </c>
-      <c r="F10">
-        <f>SUM(F3:F9)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>F10&amp;"/"&amp;C10</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>SUM(H3:H9)</f>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUM(D3:D10)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUM(E3:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUM(F3:F10)</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>F11&amp;"/"&amp;C11</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUM(H3:H10)</f>
         <v/>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5193,17 +5193,17 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>566</v>
+        <v>270</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -5226,10 +5226,10 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>200</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -5259,10 +5259,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>1462</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -5292,10 +5292,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -5325,17 +5325,17 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>6/5</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -5358,17 +5358,17 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5391,10 +5391,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>395</v>
+        <v>490</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -5427,7 +5427,7 @@
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -5658,7 +5658,7 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5721,21 +5721,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5787,7 +5787,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>50</v>
@@ -5886,21 +5886,21 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>

--- a/Midweek_Data.xlsx
+++ b/Midweek_Data.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Galatians 7" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Galatians 8" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Galatians 9" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Jesus Night Town Church" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,13 +485,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>1225</v>
+        <v>310</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -508,13 +509,13 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="E4" t="n">
-        <v>1336</v>
+        <v>659</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -532,13 +533,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>634</v>
+        <v>321</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +557,13 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>632</v>
+        <v>711</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -580,13 +581,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E7" t="n">
-        <v>2904</v>
+        <v>949</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +605,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +629,13 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E9" t="n">
-        <v>1882</v>
+        <v>1908</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -652,13 +653,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -676,13 +677,13 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>606</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -700,13 +701,13 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="E12" t="n">
-        <v>1004</v>
+        <v>3489</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -721,16 +722,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>3043</v>
+        <v>2663</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -745,16 +746,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +773,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
-        <v>1310</v>
+        <v>2875</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -796,13 +797,37 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>200</v>
+        <v>291</v>
       </c>
       <c r="E16" t="n">
-        <v>4547</v>
+        <v>5427</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jesus Night Town Church</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
+        <v>180</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -891,18 +916,18 @@
         <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>291</v>
+        <v>645</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -954,21 +979,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -987,21 +1012,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1119,21 +1144,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1152,10 +1177,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -1185,21 +1210,21 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>290</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1218,7 +1243,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
@@ -1251,10 +1276,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -1284,10 +1309,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>470</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1317,21 +1342,21 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>2730</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -1350,21 +1375,21 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -1383,21 +1408,21 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -1416,10 +1441,10 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1449,21 +1474,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -1509,7 +1534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,21 +1606,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -1611,24 +1636,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -1647,21 +1672,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>1900</v>
+        <v>1645</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -1677,24 +1702,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1710,119 +1735,119 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1833,29 +1858,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>422</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1866,128 +1891,128 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Upsa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Vacation Church</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Antoinette Annan</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/0</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Volta Annex New</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Esllah Osei</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1998,97 +2023,64 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vacation Church</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Antoinette Annan</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0/14</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C18">
-        <f>SUM(C3:C17)</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>SUM(D3:D17)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>SUM(E3:E17)</f>
-        <v/>
-      </c>
-      <c r="F18">
-        <f>SUM(F3:F17)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>F18&amp;"/"&amp;C18</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>SUM(H3:H17)</f>
+      <c r="C17">
+        <f>SUM(C3:C16)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>SUM(D3:D16)</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>SUM(E3:E16)</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>SUM(F3:F16)</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>F17&amp;"/"&amp;C17</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>SUM(H3:H16)</f>
         <v/>
       </c>
     </row>
@@ -2103,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2262,12 +2254,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>Commonwealth 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Lois Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2295,16 +2287,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2317,23 +2309,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2361,16 +2353,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Kwapong</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Eunice Owusu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2383,23 +2375,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2427,78 +2419,78 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Main Campus Hagios</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Philmorra Laryea Okorley</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2526,49 +2518,49 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Main Campus Pistis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Clement Appoh</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/5</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
+          <t>Main Campus Tsalach</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>Jennifer Aidoo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2581,23 +2573,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Main Campus Tsalach</t>
+          <t>Main campus Zogreo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jennifer Aidoo</t>
+          <t>Elinam Fiagbe</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2625,12 +2617,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Main campus Zogreo</t>
+          <t>Volta Hall</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elinam Fiagbe</t>
+          <t>Precious Antwi</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2658,64 +2650,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19">
-        <f>SUM(C3:C18)</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>SUM(D3:D18)</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>SUM(E3:E18)</f>
-        <v/>
-      </c>
-      <c r="F19">
-        <f>SUM(F3:F18)</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>F19&amp;"/"&amp;C19</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>SUM(H3:H18)</f>
+      <c r="C18">
+        <f>SUM(C3:C17)</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>SUM(D3:D17)</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>SUM(E3:E17)</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>SUM(F3:F17)</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>F18&amp;"/"&amp;C18</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>SUM(H3:H17)</f>
         <v/>
       </c>
     </row>
@@ -2802,21 +2761,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -2868,21 +2827,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>415</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -2904,7 +2863,7 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -2934,10 +2893,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2967,10 +2926,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -3000,21 +2959,21 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>250</v>
+        <v>2202</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3033,21 +2992,21 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -3066,10 +3025,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -3198,21 +3157,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>2317</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3231,21 +3190,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3261,20 +3220,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3294,24 +3253,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3333,7 +3292,7 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -3363,21 +3322,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -3393,24 +3352,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -3426,20 +3385,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -3459,24 +3418,24 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -3492,20 +3451,20 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -3521,10 +3480,10 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="E13" t="n">
-        <v>1645</v>
+        <v>4396</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -3565,6 +3524,303 @@
       </c>
       <c r="H14">
         <f>SUM(H3:H13)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Jesus Night Town Church</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Governorship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>No. Of Bacentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Att</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Income(GHS)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No. Of Services</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Services/Bacentas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Services Not Held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Adjiriganor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yves Mensah</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>110</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Haatso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Madina Estate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Madina Rawlings circle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mempeasem</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peter Tefuttor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ogbojo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Erasmus Laryea</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUM(C3:C8)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUM(D3:D8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E3:E8)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>F9&amp;"/"&amp;C9</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUM(H3:H8)</f>
         <v/>
       </c>
     </row>
@@ -3651,21 +3907,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>725</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -3684,10 +3940,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -3852,7 +4108,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -3882,21 +4138,21 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -3915,21 +4171,21 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -3948,21 +4204,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -3981,21 +4237,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>1096</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4014,21 +4270,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>278</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -4047,21 +4303,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -4179,21 +4435,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4212,21 +4468,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4245,10 +4501,10 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -4278,10 +4534,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -4338,7 +4594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4410,21 +4666,21 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4476,52 +4732,76 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>711</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Council Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6">
-        <f>SUM(C3:C5)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>SUM(D3:D5)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>SUM(E3:E5)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>SUM(F3:F5)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>F6&amp;"/"&amp;C6</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>SUM(H3:H5)</f>
+      <c r="C7">
+        <f>SUM(C3:C6)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUM(D3:D6)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUM(E3:E6)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUM(F3:F6)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7&amp;"/"&amp;C7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUM(H3:H6)</f>
         <v/>
       </c>
     </row>
@@ -4608,21 +4888,21 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2/3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -4641,21 +4921,21 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -4674,21 +4954,21 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -4707,21 +4987,21 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -4740,21 +5020,21 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -4773,10 +5053,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -4806,10 +5086,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -4832,10 +5112,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>1585</v>
+        <v>365</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -4962,21 +5242,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -5028,21 +5308,21 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5160,10 +5440,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5193,10 +5473,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -5226,21 +5506,21 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>341</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -5259,10 +5539,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -5325,21 +5605,21 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>195</v>
+        <v>716</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5358,17 +5638,17 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -5391,10 +5671,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>490</v>
+        <v>210</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -5655,21 +5935,21 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>0/3</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -5721,21 +6001,21 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -5787,10 +6067,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -5846,7 +6126,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Emmanuel Osei</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5879,7 +6159,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dennis Kpogli</t>
+          <t>Edna Avuletey</t>
         </is>
       </c>
       <c r="C13" t="n">
